--- a/ksoft/docs/records/Nota_Fiscal_Enum_Status.xlsx
+++ b/ksoft/docs/records/Nota_Fiscal_Enum_Status.xlsx
@@ -1016,13 +1016,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE6979B8-75B2-4838-8B48-C1FD31479BD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BED484-81EB-45BE-AB25-FD0F68862E71}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31028C95-51AF-4741-B8BB-6328D7DD366A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B3C9A54-5CD6-4D99-BEA4-541B12D270AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{731ECD73-58BE-460F-9541-89B1EE66B3CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D92A45D-5B3A-4D65-B952-82730D9B54C0}"/>
 </file>
--- a/ksoft/docs/records/Nota_Fiscal_Enum_Status.xlsx
+++ b/ksoft/docs/records/Nota_Fiscal_Enum_Status.xlsx
@@ -1016,13 +1016,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BED484-81EB-45BE-AB25-FD0F68862E71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE6979B8-75B2-4838-8B48-C1FD31479BD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B3C9A54-5CD6-4D99-BEA4-541B12D270AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31028C95-51AF-4741-B8BB-6328D7DD366A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D92A45D-5B3A-4D65-B952-82730D9B54C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{731ECD73-58BE-460F-9541-89B1EE66B3CF}"/>
 </file>